--- a/Arquivos_ITR/dados_acareacoes_ITR.xlsx
+++ b/Arquivos_ITR/dados_acareacoes_ITR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320071480647</t>
+          <t>3320041971196</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(STB INT) DIOVANI WALISON (BAR)</t>
+          <t>(ITR INT) JADERSON BRANDAO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,44 +481,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Samuel Silva boladao</t>
+          <t>lanna1921</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5531995957956</t>
+          <t>+5531991749824</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nossa senhora Aparecida 38 casa, Barão de Cocais</t>
+          <t>rua José Malaquias 335 casa, São Gonçalo do Rio Abaixo</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Óculos de Sol Masculino Madeira Bambu UV400*1</t>
+          <t>Saia Cintura Alta Courino Moda Rodeio Feminina com Zíper Lateral e Material Suave e Confortável Tamanhos P a GG Envio Imediato*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:27:33</t>
+          <t>2026-09-18 14:12:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320047499999</t>
+          <t>3320047982352</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(ITR LOC) BRUNO COSTA</t>
+          <t>(ITR LOC) WANDERSON JUNIOR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,267 +528,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sidiane Fernandes</t>
+          <t>Marcos Túlio Silva Ferreira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5531999065324</t>
+          <t>+5531995599938</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rua Daniel de grisolia 163, Itabira</t>
+          <t>Rua pássaro verde 7 Perto da igreja católica, Itabira</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Legging de Couro Plus Size Inverno: Forro Peluciado, Quente e Modelador!*1</t>
+          <t>Jogo De Soquete Sextavado 1/4 Catraca 12 Peças com Extensão BaiDi Original*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-09 13:26:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3320086497620</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>(STB INT) JOAO LUIZ (STB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>joaofigue1redo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>+5531997967730</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Camélia 280 Mercearia da Dinha, Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kit 3 ou 6 Pares Meias Futebol Antiderrapantes meia canela futsal*1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-09 13:25:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3320032504840</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>(STB LOC) EMANUEL FELIPE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Maria Fernanda Braga Raquel</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>+5531995333855</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rua das Margaridas 55, Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sutiã Adesivo de Silicone Invisível e Confortável Sem Alças que Aumenta e Levanta os Seios*1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-09 13:25:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3320030501275</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(STB INT) CARLOS VINICIUS E (STB)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Alana Felisberto</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+5531971480883</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Maria Diogo teixeira 203 Ao lado 202, Entregar 13 H, Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Marca Saia de Couro Preto com Fenda e Ziper Balada Inverno para Mulheres Estilo Casual Elegante*1+Marca Saia de Couro Preto com Fenda e Ziper Balada Inverno para Mulheres Estilo Casual Elegante*1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>80.7</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:53:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3320099498709</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>(ITR LOC) Sergio Almeida</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ana Luísa Ribeiro Simões</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>+5531998710470</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rua Raimundo Ramiro Lage 396 Casa, Itambé do Mato Dentro</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Cinta Modeladora Feminina Redutora Abdominal/Afina a Cintura/Fitness*1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-09 10:52:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3320013493582</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ELIETE APARECIDA DA CRUZ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bruno Luiz</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>+5586981011625</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>rua Padre Teles 425 kitnet, Barão de Cocais</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Aquecedor De Ar De Ambiente Quartzo 36cm 127/220v - Cinza*1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>107.15</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:22:06</t>
+          <t>2026-09-18 14:12:36</t>
         </is>
       </c>
     </row>
